--- a/EKG_Kalite_Yönetim_Sistemi/07_Standart İş ve Uygunsuz Ürün/02_SW2 - Yeniden İşleme ve Özel Proses/EKG-URT-FRM-16_yeniden_isleme_ve_akisa_donus_kayit_formu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/07_Standart İş ve Uygunsuz Ürün/02_SW2 - Yeniden İşleme ve Özel Proses/EKG-URT-FRM-16_yeniden_isleme_ve_akisa_donus_kayit_formu.xlsx
@@ -950,7 +950,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-URT-FRM-16&amp;C&amp;"Arial,Regular"&amp;11Yeniden İşleme ve Akışa Dönüş Kayıt Formu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 22.09.2026
+Revizyon nedeni: Ürün bazlı akışa dönüş formu temel işlem ve kontrol kanıtı/kararıyla düzenlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>